--- a/output/北塩原村_将来推計.xlsx
+++ b/output/北塩原村_将来推計.xlsx
@@ -695,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -928,56 +928,64 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>【注意（令和8年10月10日）】本ブックの手帳所持者数の中位推計（令和11年度 合計145人）は、平成31年〜令和5年の減少傾向を延ばしたものです。他メンバー版の正本 第2章2により、令和8年4月の実績が181人（身体127・療育16・精神38）で令和5年の156人から25人増えていることが分かりました。減少を前提とした推計は成り立ちません。令和6年・令和7年の実績を村から受領したうえで、第2次算定で推計をやり直してください。それまで令和11年度の推計値を計画書・概要版に載せないこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>本ブックの使い方</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>1. 黄色のセル（入力欄）に村から受領した令和6〜8年度の実績を入力します。他のセルは数式のため触りません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2. 手帳所持者数の実績を入力すると、トレンド延長法の回帰対象年数が自動的に増え、推計値が更新されます。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3. 所持率法の基準年（03_手帳将来推計 C4）は、最新実績が揃った年度に変更します。基準年の総人口は01_人口推計から自動参照します。</t>
+          <t>1. 黄色のセル（入力欄）に村から受領した令和6〜8年度の実績を入力します。他のセルは数式のため触りません。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>4. 令和2〜4年及び令和7〜10年の人口実績が判明した場合は、01_人口推計の該当行に入力します（補間推計を実績で上書き）。</t>
+          <t>2. 手帳所持者数の実績を入力すると、トレンド延長法の回帰対象年数が自動的に増え、推計値が更新されます。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>3. 所持率法の基準年（03_手帳将来推計 C4）は、最新実績が揃った年度に変更します。基準年の総人口は01_人口推計から自動参照します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>4. 令和2〜4年及び令和7〜10年の人口実績が判明した場合は、01_人口推計の該当行に入力します（補間推計を実績で上書き）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>5. 推計結果は計画書 第2章に転記します。単一値ではなく方法A・方法Bの幅を併記してください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
   </mergeCells>
@@ -4295,7 +4303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4349,12 +4357,12 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>令和6〜8年度の手帳所持者数</t>
+          <t>令和6年度・令和7年度の手帳所持者数</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>身体・療育・精神の各年4月1日現在の所持者数。</t>
+          <t>身体・療育・精神の各年4月1日現在の所持者数。令和8年4月の値は他メンバー版の正本（第2章2）により判明した（身体127人・療育16人・精神38人＝181人）。残るのは令和6年・令和7年。</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -4364,7 +4372,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
       <c r="E6" s="50" t="inlineStr">
@@ -4457,71 +4465,71 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>調査対象者数と手帳所持者数の差異</t>
+          <t>【解消】調査対象者数と手帳所持者数の差異</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>仕様書の約190人（身体約130・精神約40・療育約20）と、現行計画の156人（令和5年）の差の理由。集計基準・対象年齢・サービス利用者の重複計上の違いを確認する。</t>
+          <t>仕様書の約190人（身体約130・精神約40・療育約20）は、令和8年4月の実績181人（身体127・療育16・精神38）とほぼ一致する。概数の見込みではなく、令和8年時点の実数であったと考えられる。集計基準の違いではないため、この確認事項は解消とする。</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02_手帳実績／アンケート発送設計</t>
+          <t>02_手帳実績</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="E10" s="50" t="inlineStr">
-        <is>
-          <t>村資料待ち</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>解消（正本 第2章2による）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>村独自の人口ビジョン・将来推計</t>
+          <t>令和11年度の中位推計のやり直し</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>総合振興計画の人口ビジョン、社人研推計等がある場合はその数値。</t>
+          <t>本ブックの中位推計（合計145人）は平成31年〜令和5年の減少を延ばしたものである。令和8年4月の実績181人は令和5年の156人から25人増えており、減少を前提とした推計は成り立たない。令和6年・令和7年の実績を受領したうえで、第2次算定で推計をやり直す。概要版は令和11年度の見通しを載せず、やり直す旨を注記した。</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>01_人口推計／06_推計方法</t>
+          <t>03_手帳将来推計／概要版 第5節</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E11" s="50" t="inlineStr">
-        <is>
-          <t>村資料待ち</t>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>令和6・7年の実績待ち</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>身体障害者手帳の減少要因</t>
+          <t>村独自の人口ビジョン・将来推計</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>老年人口が横ばい〜微減である一方、身体障害者手帳所持者数が減少している要因。手帳更新時期・制度改正・転出入・死亡等の影響を確認する。</t>
+          <t>総合振興計画の人口ビジョン、社人研推計等がある場合はその数値。</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>03_手帳将来推計／04_推計の不確実性</t>
+          <t>01_人口推計／06_推計方法</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -4538,17 +4546,17 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>精神障害者保健福祉手帳の増加要因</t>
+          <t>身体障害者手帳の減少要因</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>所持者数・所持率とも増加傾向にある背景（受診機会の広がり、相談体制、新規申請の動向等）。</t>
+          <t>老年人口が横ばい〜微減である一方、身体障害者手帳所持者数が減少している要因。手帳更新時期・制度改正・転出入・死亡等の影響を確認する。</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>03_手帳将来推計／相談支援施策</t>
+          <t>03_手帳将来推計／04_推計の不確実性</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -4565,25 +4573,52 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>精神障害者保健福祉手帳の増加要因</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>所持者数・所持率とも増加傾向にある背景（受診機会の広がり、相談体制、新規申請の動向等）。</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>03_手帳将来推計／相談支援施策</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E14" s="50" t="inlineStr">
+        <is>
+          <t>村資料待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
           <t>障がい児の就学状況</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>特別支援学校・特別支援学級の在籍者数（令和8年4月1日現在）、卒業予定年度。</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>計画書 第2章／障がい児福祉計画</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E14" s="50" t="inlineStr">
+      <c r="E15" s="50" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>

--- a/output/北塩原村_将来推計.xlsx
+++ b/output/北塩原村_将来推計.xlsx
@@ -928,10 +928,10 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="76" customHeight="1">
+    <row r="13" ht="110" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>【注意（令和8年10月10日）】本ブックの手帳所持者数の中位推計（令和11年度 合計145人）は、平成31年〜令和5年の減少傾向を延ばしたものです。他メンバー版の正本 第2章2により、令和8年4月の実績が181人（身体127・療育16・精神38）で令和5年の156人から25人増えていることが分かりました。減少を前提とした推計は成り立ちません。令和6年・令和7年の実績を村から受領したうえで、第2次算定で推計をやり直してください。それまで令和11年度の推計値を計画書・概要版に載せないこと。</t>
+          <t>【注意（令和8年10月13日 改訂）】本ブックの手帳所持者数の中位推計（令和11年度 合計145人）は、平成31年〜令和5年の減少傾向を延ばしたものです。他メンバー版の正本 第2章2は令和8年4月を181人（身体127・療育16・精神38）と記述していますが、他メンバー版のワークシートの注記は「総数はR2〜R5が第7期計画（4月1日）、R6〜R8は推計」であり、村の台帳による確定値ではありません（北塩原村_他メンバー素案_網羅性点検.xlsx）。したがって、減少を前提とした推計が成り立つかどうかを現時点では確かめられません。令和8年10月10日の本注記は「実績181人により減少の前提が崩れた」と書いていましたが、仮置き値を実績として扱っていたため改めました。令和6年・令和7年・令和8年の実数を村の手帳台帳から受領したうえで（Ｍ-113）、第2次算定で推計をやり直してください。令和11年の合計は仮説の置き方により139人から206人まで67人の幅があります（北塩原村_レビュー対応_第3回.xlsx 02_手帳推計）。それまで令和11年度の推計値を計画書・概要版に載せないこと。</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4357,12 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の手帳所持者数</t>
+          <t>令和6・7・8年度の手帳所持者数（Ｍ-113）</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>身体・療育・精神の各年4月1日現在の所持者数。令和8年4月の値は他メンバー版の正本（第2章2）により判明した（身体127人・療育16人・精神38人＝181人）。残るのは令和6年・令和7年。</t>
+          <t>身体・療育・精神の各年4月1日現在の所持者数と、その出所。正本（第2章2）の令和8年4月の値（身体127人・療育16人・精神38人＝181人）は、他メンバー版のワークシートでは「R6〜R8は推計」と注記された仮置き値であり、村の台帳による確定値ではない。令和8年も含めて照会する。平成31年〜令和5年（現行計画本編）と同じ数え方であるかもあわせて確かめる（村外の施設に入所している方等の取扱い）。</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -4465,12 +4465,12 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>【解消】調査対象者数と手帳所持者数の差異</t>
+          <t>【解消を取り消し】調査対象者数と手帳所持者数の差異</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>仕様書の約190人（身体約130・精神約40・療育約20）は、令和8年4月の実績181人（身体127・療育16・精神38）とほぼ一致する。概数の見込みではなく、令和8年時点の実数であったと考えられる。集計基準の違いではないため、この確認事項は解消とする。</t>
+          <t>令和8年10月10日に、仕様書の約190人（身体約130・精神約40・療育約20）は正本 第2章2 の181人とほぼ一致するので実数であったと考えられる、として解消していた。しかし正本の181人は、他メンバー版のワークシートでは令和6〜8年が推計と注記されており、その推計の目安が仕様書の約190人そのものである。約190人で作った値を根拠に約190人を実数と結論しており循環していた。令和8年10月13日に解消を取り消す。</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>最優先</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>解消（正本 第2章2による）</t>
+          <t>未解消（Ｍ-113で照会）</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>本ブックの中位推計（合計145人）は平成31年〜令和5年の減少を延ばしたものである。令和8年4月の実績181人は令和5年の156人から25人増えており、減少を前提とした推計は成り立たない。令和6年・令和7年の実績を受領したうえで、第2次算定で推計をやり直す。概要版は令和11年度の見通しを載せず、やり直す旨を注記した。</t>
+          <t>本ブックの中位推計（合計145人）は平成31年〜令和5年の減少を延ばしたものである。正本 第2章2 の181人は仮置き値であるため、減少を前提とした推計が成り立つかどうかを確かめられない。令和6・7・8年の実数を村の手帳台帳から受領したうえで、第2次算定で推計をやり直す。令和11年の合計は仮説の置き方により139人から206人まで67人の幅がある（レビュー対応_第3回 02_手帳推計）。概要版は令和11年度の見通しを載せず、やり直す旨を注記した。</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>令和6・7年の実績待ち</t>
+          <t>Ｍ-113の回答待ち</t>
         </is>
       </c>
     </row>
